--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_FULL\SuppXLS\Policy_1\Dobre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juane\Documents\Master UPC\2 Energy Modelling and Climate Policy\TIMES Project\Msc_SELECT_VEDA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F785791-9CB0-4EE1-816B-CC1CB2B4ADB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1BE7B8-6986-4A01-B114-54A1091D26ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FLO_SUBSIDY" sheetId="2" r:id="rId1"/>
@@ -723,28 +723,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
@@ -767,15 +767,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
@@ -784,7 +784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>6</v>
       </c>
@@ -792,7 +792,7 @@
         <v>2050</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -801,7 +801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>6</v>
       </c>
@@ -827,6 +827,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -835,15 +844,6 @@
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,6 +1090,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82319D87-9F89-465F-A992-21F87A25DE83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -1102,14 +1110,6 @@
     <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juane\Documents\Master UPC\2 Energy Modelling and Climate Policy\TIMES Project\Msc_SELECT_VEDA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1BE7B8-6986-4A01-B114-54A1091D26ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C596F69-3C07-4517-9785-602DE9F5054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
         <v>2023</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
@@ -792,7 +792,7 @@
         <v>2050</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -827,15 +827,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -844,6 +835,15 @@
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,14 +1090,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82319D87-9F89-465F-A992-21F87A25DE83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -1110,6 +1102,14 @@
     <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
+++ b/SuppXLS/Scen_SUBSIDY_RES_CONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juane\Documents\Master UPC\2 Energy Modelling and Climate Policy\TIMES Project\Msc_SELECT_VEDA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C596F69-3C07-4517-9785-602DE9F5054A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77DB6B4-1970-422B-964E-3A37763A2672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,7 +775,7 @@
         <v>2023</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
@@ -792,7 +792,7 @@
         <v>2050</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -827,6 +827,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -835,15 +844,6 @@
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,6 +1090,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82319D87-9F89-465F-A992-21F87A25DE83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -1102,14 +1110,6 @@
     <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{701208FD-3905-4372-97B8-23942D25C431}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
